--- a/output/pdf_financials_xlsx/CLDV.xlsx
+++ b/output/pdf_financials_xlsx/CLDV.xlsx
@@ -2225,16 +2225,16 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.102309</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.112757</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.527649</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>2.079317</v>
       </c>
     </row>
     <row r="93">
@@ -3602,7 +3602,11 @@
           <t>Reserves 11</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
@@ -4120,7 +4124,11 @@
           <t>Reserves 12</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E29" s="5" t="n">
         <v>0.102309</v>
       </c>

--- a/output/pdf_financials_xlsx/CLDV.xlsx
+++ b/output/pdf_financials_xlsx/CLDV.xlsx
@@ -660,13 +660,13 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.008496</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.016116</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.002776</v>
       </c>
     </row>
     <row r="13">
@@ -963,13 +963,13 @@
         <v>-0.467208</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.850081</v>
+        <v>-0.858577</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-3.301357</v>
+        <v>-3.317473</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.529329</v>
+        <v>-0.5321050000000001</v>
       </c>
     </row>
     <row r="28">
@@ -1001,13 +1001,13 @@
         <v>-0.467208</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.837998</v>
+        <v>-0.846494</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-3.253027</v>
+        <v>-3.269143</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.529329</v>
+        <v>-0.5321050000000001</v>
       </c>
     </row>
     <row r="30">
@@ -1022,7 +1022,7 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-1736.423539162868</v>
+        <v>-1754.02818068794</v>
       </c>
       <c r="D30" s="1" t="inlineStr">
         <is>
@@ -1093,16 +1093,16 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.329932</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.790514</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.002525</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.001563</v>
       </c>
     </row>
     <row r="35">
@@ -1131,16 +1131,16 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.329932</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.790514</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.002525</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.001563</v>
       </c>
     </row>
     <row r="37">
@@ -1359,16 +1359,16 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.406227</v>
+        <v>0.076295</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.9400539999999999</v>
+        <v>0.14954</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.080633</v>
+        <v>0.078108</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.887784</v>
+        <v>0.886221</v>
       </c>
     </row>
     <row r="49">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -6456,7 +6456,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -8286,7 +8286,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -8326,7 +8326,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">

--- a/output/pdf_financials_xlsx/CLDV.xlsx
+++ b/output/pdf_financials_xlsx/CLDV.xlsx
@@ -556,16 +556,16 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.506929</v>
+        <v>0.509578</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.37615</v>
+        <v>0.396611</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.13982</v>
+        <v>0.449696</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.056681</v>
+        <v>0.057505</v>
       </c>
     </row>
     <row r="8">
@@ -2393,7 +2393,7 @@
         <v>-0.013656</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>0.017811</v>
+        <v>0.044205</v>
       </c>
     </row>
     <row r="102">
@@ -2488,7 +2488,7 @@
         <v>0.076419</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>0.219432</v>
+        <v>0.245826</v>
       </c>
     </row>
     <row r="107">
@@ -4732,7 +4732,11 @@
           <t>Provision for GST receivable</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
           <t>-</t>
@@ -6172,7 +6176,11 @@
           <t>Office expenses</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr"/>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E86" t="inlineStr">
         <is>
           <t>-</t>
@@ -8070,7 +8078,11 @@
           <t>Office expense</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr"/>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E139" s="5" t="n">
         <v>0.002649</v>
       </c>
